--- a/Elli/results_week_v5_resources.xlsx
+++ b/Elli/results_week_v5_resources.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="128">
   <si>
     <t>student_id</t>
   </si>
@@ -326,31 +326,19 @@
     <t>https://youtu.be/K5KVEU3aaeQ</t>
   </si>
   <si>
-    <t>Ποια είναι η τελευταία μεταβλητή ή συνάρτηση πριν από το runtime error;</t>
-  </si>
-  <si>
-    <t>Ποιον κανόνα σύνταξης παραβιάζει η γραμμή 1;</t>
-  </si>
-  <si>
-    <t>Ποιον κανόνα σύνταξης παραβιάζει η γραμμή 10;</t>
-  </si>
-  <si>
     <t>Ποιον κανόνα σύνταξης παραβιάζει η γραμμή 23;</t>
   </si>
   <si>
     <t>beginner</t>
   </si>
   <si>
-    <t>Δοκίμασε τον κώδικα με μία πολύ μικρή είσοδο και κατέγραψε τις τιμές.</t>
-  </si>
-  <si>
     <t>Διόρθωσε πρώτα μία μικρή εκδοχή του ίδιου συντακτικού λάθους.</t>
   </si>
   <si>
     <t>[]</t>
   </si>
   <si>
-    <t>agent_unavailable: RuntimeError: Λείπει το GEMINI_API_KEY environment variable.</t>
+    <t>agent_error: ClientError: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-3.6-flash\nPlease retry in 531.266211ms.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-3.6-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '0s'}]}}</t>
   </si>
   <si>
     <t>Ομάδα υψηλής ανάγκης υποστήριξης</t>
@@ -1098,31 +1086,31 @@
         <v>102</v>
       </c>
       <c r="BC2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="BD2" t="s">
         <v>103</v>
       </c>
       <c r="BE2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>105</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH2" t="s">
         <v>107</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BI2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ2">
+        <v>0</v>
+      </c>
+      <c r="BK2" t="s">
         <v>108</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>110</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>111</v>
-      </c>
-      <c r="BI2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BJ2">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:63">
@@ -1286,23 +1274,23 @@
         <v>102</v>
       </c>
       <c r="BC3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="BD3" t="s">
+        <v>103</v>
+      </c>
+      <c r="BE3" t="s">
         <v>104</v>
       </c>
-      <c r="BE3" t="s">
+      <c r="BF3" t="s">
+        <v>105</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH3" t="s">
         <v>107</v>
       </c>
-      <c r="BF3" t="s">
-        <v>109</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>110</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>111</v>
-      </c>
       <c r="BI3" t="b">
         <v>1</v>
       </c>
@@ -1310,7 +1298,7 @@
         <v>1</v>
       </c>
       <c r="BK3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:63">
@@ -1477,20 +1465,20 @@
         <v>87</v>
       </c>
       <c r="BD4" t="s">
+        <v>103</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>104</v>
+      </c>
+      <c r="BF4" t="s">
         <v>105</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BG4" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH4" t="s">
         <v>107</v>
       </c>
-      <c r="BF4" t="s">
-        <v>109</v>
-      </c>
-      <c r="BG4" t="s">
-        <v>110</v>
-      </c>
-      <c r="BH4" t="s">
-        <v>111</v>
-      </c>
       <c r="BI4" t="b">
         <v>1</v>
       </c>
@@ -1498,7 +1486,7 @@
         <v>1</v>
       </c>
       <c r="BK4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:63">
@@ -1662,23 +1650,23 @@
         <v>102</v>
       </c>
       <c r="BC5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="BD5" t="s">
+        <v>103</v>
+      </c>
+      <c r="BE5" t="s">
         <v>104</v>
       </c>
-      <c r="BE5" t="s">
+      <c r="BF5" t="s">
+        <v>105</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH5" t="s">
         <v>107</v>
       </c>
-      <c r="BF5" t="s">
-        <v>109</v>
-      </c>
-      <c r="BG5" t="s">
-        <v>110</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>111</v>
-      </c>
       <c r="BI5" t="b">
         <v>1</v>
       </c>
@@ -1686,7 +1674,7 @@
         <v>1</v>
       </c>
       <c r="BK5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:63">
@@ -1838,22 +1826,22 @@
         <v>102</v>
       </c>
       <c r="BC6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="BD6" t="s">
         <v>103</v>
       </c>
       <c r="BE6" t="s">
+        <v>104</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>105</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH6" t="s">
         <v>107</v>
-      </c>
-      <c r="BF6" t="s">
-        <v>108</v>
-      </c>
-      <c r="BG6" t="s">
-        <v>110</v>
-      </c>
-      <c r="BH6" t="s">
-        <v>111</v>
       </c>
       <c r="BI6" t="b">
         <v>1</v>
@@ -1862,7 +1850,7 @@
         <v>2</v>
       </c>
       <c r="BK6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:63">
@@ -2026,23 +2014,23 @@
         <v>102</v>
       </c>
       <c r="BC7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="BD7" t="s">
+        <v>103</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>104</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>105</v>
+      </c>
+      <c r="BG7" t="s">
         <v>106</v>
       </c>
-      <c r="BE7" t="s">
+      <c r="BH7" t="s">
         <v>107</v>
       </c>
-      <c r="BF7" t="s">
-        <v>109</v>
-      </c>
-      <c r="BG7" t="s">
-        <v>110</v>
-      </c>
-      <c r="BH7" t="s">
-        <v>111</v>
-      </c>
       <c r="BI7" t="b">
         <v>1</v>
       </c>
@@ -2050,7 +2038,7 @@
         <v>1</v>
       </c>
       <c r="BK7" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:63">
@@ -2202,31 +2190,31 @@
         <v>102</v>
       </c>
       <c r="BC8" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="BD8" t="s">
         <v>103</v>
       </c>
       <c r="BE8" t="s">
+        <v>104</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>105</v>
+      </c>
+      <c r="BG8" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH8" t="s">
         <v>107</v>
       </c>
-      <c r="BF8" t="s">
+      <c r="BI8" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="s">
         <v>108</v>
-      </c>
-      <c r="BG8" t="s">
-        <v>110</v>
-      </c>
-      <c r="BH8" t="s">
-        <v>111</v>
-      </c>
-      <c r="BI8" t="b">
-        <v>1</v>
-      </c>
-      <c r="BJ8">
-        <v>0</v>
-      </c>
-      <c r="BK8" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:63">
@@ -2393,20 +2381,20 @@
         <v>87</v>
       </c>
       <c r="BD9" t="s">
+        <v>103</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>104</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>105</v>
+      </c>
+      <c r="BG9" t="s">
         <v>106</v>
       </c>
-      <c r="BE9" t="s">
+      <c r="BH9" t="s">
         <v>107</v>
       </c>
-      <c r="BF9" t="s">
-        <v>109</v>
-      </c>
-      <c r="BG9" t="s">
-        <v>110</v>
-      </c>
-      <c r="BH9" t="s">
-        <v>111</v>
-      </c>
       <c r="BI9" t="b">
         <v>1</v>
       </c>
@@ -2414,7 +2402,7 @@
         <v>1</v>
       </c>
       <c r="BK9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -2439,31 +2427,31 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B4">
         <v>12</v>
@@ -2479,7 +2467,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B6">
         <v>8</v>
@@ -2487,7 +2475,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B7">
         <v>11.88</v>
@@ -2495,7 +2483,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -2503,7 +2491,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B9">
         <v>3</v>
@@ -2511,7 +2499,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B10" t="b">
         <v>1</v>
@@ -2519,31 +2507,31 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B12" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B13" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B14" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
